--- a/Prueba_Carga_Masiva_250_registros_Asincrono.xlsx
+++ b/Prueba_Carga_Masiva_250_registros_Asincrono.xlsx
@@ -14474,7 +14474,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VERSION_PLANTILLA: 2.0.0</v>
+        <v>VERSION_PLANTILLA: 2.1.0</v>
       </c>
     </row>
     <row r="3">
